--- a/knowledge/shared/templates/raw/AcuvimIIR_v1.01_20260509.xlsx
+++ b/knowledge/shared/templates/raw/AcuvimIIR_v1.01_20260509.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://accuenergycom.sharepoint.com/sites/CN-Project-AcuHMI/Shared Documents/PX-EMD-G/13 项目各领域交付件/06 PM(产品)/02 商业需求规格书/参数类区分/模板管理/AcuvimIIR&amp;PXE1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="245" documentId="13_ncr:1_{D127FE2E-232C-4A3E-933F-C2503FCBA3F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35BEA8BB-8287-427C-B5A9-6276C8976EAE}"/>
+  <xr:revisionPtr revIDLastSave="248" documentId="13_ncr:1_{D127FE2E-232C-4A3E-933F-C2503FCBA3F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73E0050E-8653-44AB-9DB4-BBC91EB58CC3}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4885" uniqueCount="1283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4887" uniqueCount="1283">
   <si>
     <t>isOnline</t>
   </si>
@@ -17487,7 +17487,12 @@
       </c>
       <c r="I306" s="21"/>
       <c r="J306" s="44"/>
-      <c r="T306" s="45"/>
+      <c r="R306" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="T306" s="45" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="307" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="43">
@@ -27822,6 +27827,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="87eaac2d-a5f8-4c7f-abd5-4f93f35bdb19" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4da14e33-fb1f-428b-aede-7872bd2aa051">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002BBB7D409CEECF4A817F9E6F5E594B2C" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="37f143e3fdc1fa3b63685f0ff13c642a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4da14e33-fb1f-428b-aede-7872bd2aa051" xmlns:ns3="87eaac2d-a5f8-4c7f-abd5-4f93f35bdb19" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="059c814d4ac4e7b6ff94b32f8c089d49" ns2:_="" ns3:_="">
     <xsd:import namespace="4da14e33-fb1f-428b-aede-7872bd2aa051"/>
@@ -28022,28 +28047,21 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="87eaac2d-a5f8-4c7f-abd5-4f93f35bdb19" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4da14e33-fb1f-428b-aede-7872bd2aa051">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{281EF608-CBE4-485E-882E-C25F1E5E308D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BA6F056-3B1C-4FDC-AF88-47374440FAF3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="4da14e33-fb1f-428b-aede-7872bd2aa051"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="87eaac2d-a5f8-4c7f-abd5-4f93f35bdb19"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -28055,18 +28073,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BA6F056-3B1C-4FDC-AF88-47374440FAF3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{281EF608-CBE4-485E-882E-C25F1E5E308D}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4da14e33-fb1f-428b-aede-7872bd2aa051"/>
+    <ds:schemaRef ds:uri="87eaac2d-a5f8-4c7f-abd5-4f93f35bdb19"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="87eaac2d-a5f8-4c7f-abd5-4f93f35bdb19"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="4da14e33-fb1f-428b-aede-7872bd2aa051"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>